--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -509,13 +509,13 @@
         <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>2232</v>
+        <v>2264</v>
       </c>
       <c r="E3" t="n">
-        <v>2296</v>
+        <v>2328</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9721</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="4">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>3370</v>
       </c>
       <c r="E4" t="n">
-        <v>3365</v>
+        <v>3370</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -579,10 +579,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="E6" t="n">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0.9993000000000001</v>
@@ -691,13 +691,13 @@
         <v>423</v>
       </c>
       <c r="D11" t="n">
-        <v>2053</v>
+        <v>2059</v>
       </c>
       <c r="E11" t="n">
-        <v>2476</v>
+        <v>2482</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8292</v>
+        <v>0.8295999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -737,10 +737,10 @@
         <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>3589</v>
+        <v>3595</v>
       </c>
       <c r="E13" t="n">
-        <v>3629</v>
+        <v>3635</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0.9890000000000001</v>
@@ -761,10 +761,10 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>6764</v>
+        <v>6779</v>
       </c>
       <c r="E14" t="n">
-        <v>6806</v>
+        <v>6821</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.9937999999999999</v>

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$15</definedName>
@@ -506,16 +506,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>2264</v>
+        <v>2261</v>
       </c>
       <c r="E3" t="n">
-        <v>2328</v>
+        <v>2296</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9725</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="4">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="E4" t="n">
-        <v>3370</v>
+        <v>3365</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="E6" t="n">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D11" t="n">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="E11" t="n">
-        <v>2482</v>
+        <v>2476</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0.8295999999999999</v>
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3595</v>
+        <v>3626</v>
       </c>
       <c r="E13" t="n">
-        <v>3635</v>
+        <v>3629</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="14">
@@ -761,10 +761,10 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>6779</v>
+        <v>6764</v>
       </c>
       <c r="E14" t="n">
-        <v>6821</v>
+        <v>6806</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0.9937999999999999</v>

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>381</v>
       </c>
       <c r="D3" t="n">
-        <v>2261</v>
+        <v>782</v>
       </c>
       <c r="E3" t="n">
-        <v>2296</v>
+        <v>1163</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9848</v>
+        <v>0.6724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>3365</v>
+        <v>3200</v>
       </c>
       <c r="E4" t="n">
-        <v>3365</v>
+        <v>3228</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2738</v>
+        <v>2643</v>
       </c>
       <c r="E6" t="n">
-        <v>2738</v>
+        <v>2643</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,20 +666,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>94</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9893999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,22 +690,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>422</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
-        <v>2054</v>
+        <v>1938</v>
       </c>
       <c r="E11" t="n">
-        <v>2476</v>
+        <v>1978</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.8295999999999999</v>
+        <v>0.9798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -725,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -734,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3626</v>
+        <v>3212</v>
       </c>
       <c r="E13" t="n">
-        <v>3629</v>
+        <v>3216</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9992</v>
+        <v>0.9987999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -758,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>6764</v>
+        <v>4846</v>
       </c>
       <c r="E14" t="n">
-        <v>6806</v>
+        <v>4848</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9937999999999999</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>381</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>782</v>
+        <v>1243</v>
       </c>
       <c r="E3" t="n">
-        <v>1163</v>
+        <v>1257</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6724</v>
+        <v>0.9889</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>3200</v>
+        <v>2797</v>
       </c>
       <c r="E4" t="n">
-        <v>3228</v>
+        <v>2885</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9913</v>
+        <v>0.9695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2643</v>
+        <v>1429</v>
       </c>
       <c r="E6" t="n">
-        <v>2643</v>
+        <v>1429</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,22 +666,22 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>54</v>
+      </c>
+      <c r="E10" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>93</v>
-      </c>
-      <c r="E10" t="n">
-        <v>94</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.9893999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1938</v>
+        <v>986</v>
       </c>
       <c r="E11" t="n">
-        <v>1978</v>
+        <v>986</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9798</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3212</v>
+        <v>1925</v>
       </c>
       <c r="E13" t="n">
-        <v>3216</v>
+        <v>1925</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9987999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>4846</v>
+        <v>3351</v>
       </c>
       <c r="E14" t="n">
-        <v>4848</v>
+        <v>3351</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1243</v>
+        <v>1028</v>
       </c>
       <c r="E3" t="n">
-        <v>1257</v>
+        <v>1029</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9889</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88</v>
+        <v>202</v>
       </c>
       <c r="D4" t="n">
-        <v>2797</v>
+        <v>1929</v>
       </c>
       <c r="E4" t="n">
-        <v>2885</v>
+        <v>2131</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9695</v>
+        <v>0.9052</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1429</v>
+        <v>1301</v>
       </c>
       <c r="E6" t="n">
-        <v>1429</v>
+        <v>1301</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>1145</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>1145</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>986</v>
+        <v>90</v>
       </c>
       <c r="E11" t="n">
-        <v>986</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1925</v>
+        <v>1535</v>
       </c>
       <c r="E13" t="n">
-        <v>1925</v>
+        <v>1541</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>3351</v>
+        <v>4387</v>
       </c>
       <c r="E14" t="n">
-        <v>3351</v>
+        <v>4402</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
+        <v>0.9965999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>1028</v>
+        <v>951</v>
       </c>
       <c r="E3" t="n">
-        <v>1029</v>
+        <v>1008</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9434999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1929</v>
+        <v>2294</v>
       </c>
       <c r="E4" t="n">
-        <v>2131</v>
+        <v>2294</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9052</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>995</v>
       </c>
       <c r="E6" t="n">
-        <v>1301</v>
+        <v>1026</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1145</v>
+        <v>1086</v>
       </c>
       <c r="E10" t="n">
-        <v>1145</v>
+        <v>1086</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E11" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>1535</v>
+        <v>1294</v>
       </c>
       <c r="E13" t="n">
-        <v>1541</v>
+        <v>1404</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9961</v>
+        <v>0.9217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>4387</v>
+        <v>3470</v>
       </c>
       <c r="E14" t="n">
-        <v>4402</v>
+        <v>3491</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9965999999999999</v>
+        <v>0.9940000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>951</v>
+        <v>309</v>
       </c>
       <c r="E3" t="n">
-        <v>1008</v>
+        <v>309</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9434999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>2294</v>
+        <v>1024</v>
       </c>
       <c r="E4" t="n">
-        <v>2294</v>
+        <v>1037</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>995</v>
+        <v>160</v>
       </c>
       <c r="E6" t="n">
-        <v>1026</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9698</v>
+        <v>0.9248999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1086</v>
+        <v>266</v>
       </c>
       <c r="E10" t="n">
-        <v>1086</v>
+        <v>266</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1294</v>
+        <v>396</v>
       </c>
       <c r="E13" t="n">
-        <v>1404</v>
+        <v>396</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9217</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" t="n">
-        <v>3470</v>
+        <v>1216</v>
       </c>
       <c r="E14" t="n">
-        <v>3491</v>
+        <v>1233</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9940000000000001</v>
+        <v>0.9862000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>309</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1037</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9875</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +572,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>173</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9248999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +629,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +651,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -669,19 +663,17 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>266</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,19 +685,17 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -739,19 +729,17 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>396</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1216</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1233</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9862000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2063</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2063</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3774</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>3984</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9473</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -575,17 +579,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2410</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>2410</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,17 +669,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>1880</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +693,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>299</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -726,20 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3180</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>3277</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9704</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1766</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>6572</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.7313</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2063</v>
+        <v>1900</v>
       </c>
       <c r="E3" t="n">
-        <v>2063</v>
+        <v>1901</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>210</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n">
-        <v>3774</v>
+        <v>3534</v>
       </c>
       <c r="E4" t="n">
-        <v>3984</v>
+        <v>3626</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9473</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2410</v>
+        <v>1924</v>
       </c>
       <c r="E6" t="n">
-        <v>2410</v>
+        <v>1925</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,22 +666,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1880</v>
+        <v>1530</v>
       </c>
       <c r="E10" t="n">
-        <v>1880</v>
+        <v>1534</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="E11" t="n">
-        <v>299</v>
+        <v>127</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -705,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +736,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>3180</v>
+        <v>2184</v>
       </c>
       <c r="E13" t="n">
-        <v>3277</v>
+        <v>2230</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9704</v>
+        <v>0.9793999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1766</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>4806</v>
+        <v>6350</v>
       </c>
       <c r="E14" t="n">
-        <v>6572</v>
+        <v>6365</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.7313</v>
+        <v>0.9976</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="D3" t="n">
-        <v>1900</v>
+        <v>1145</v>
       </c>
       <c r="E3" t="n">
-        <v>1901</v>
+        <v>1223</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>3534</v>
+        <v>2297</v>
       </c>
       <c r="E4" t="n">
-        <v>3626</v>
+        <v>2308</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>0.9952</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1924</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1925</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,20 +644,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -666,22 +668,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1530</v>
+        <v>1159</v>
       </c>
       <c r="E10" t="n">
-        <v>1534</v>
+        <v>1165</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9948</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -693,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -705,7 +707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -714,20 +716,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
+        <v>188</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>2184</v>
+        <v>1918</v>
       </c>
       <c r="E13" t="n">
-        <v>2230</v>
+        <v>1943</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9793999999999999</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>6350</v>
+        <v>4012</v>
       </c>
       <c r="E14" t="n">
-        <v>6365</v>
+        <v>4023</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9976</v>
+        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>1145</v>
+        <v>1319</v>
       </c>
       <c r="E3" t="n">
-        <v>1223</v>
+        <v>1335</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9362</v>
+        <v>0.988</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2297</v>
+        <v>2266</v>
       </c>
       <c r="E4" t="n">
-        <v>2308</v>
+        <v>2270</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9952</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1158</v>
+        <v>1195</v>
       </c>
       <c r="E6" t="n">
-        <v>1158</v>
+        <v>1201</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,13 +644,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1159</v>
+        <v>1134</v>
       </c>
       <c r="E10" t="n">
-        <v>1165</v>
+        <v>1134</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9948</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>188</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1918</v>
+        <v>1824</v>
       </c>
       <c r="E13" t="n">
-        <v>1943</v>
+        <v>1824</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9871</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>4012</v>
+        <v>3727</v>
       </c>
       <c r="E14" t="n">
-        <v>4023</v>
+        <v>3821</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.9754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1319</v>
+        <v>1136</v>
       </c>
       <c r="E3" t="n">
-        <v>1335</v>
+        <v>1136</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.988</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2266</v>
+        <v>1802</v>
       </c>
       <c r="E4" t="n">
-        <v>2270</v>
+        <v>1802</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1195</v>
+        <v>984</v>
       </c>
       <c r="E6" t="n">
-        <v>1201</v>
+        <v>986</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.995</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,20 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>69</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.971</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,13 +646,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -659,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>1134</v>
+        <v>998</v>
       </c>
       <c r="E10" t="n">
-        <v>1134</v>
+        <v>1015</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -707,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -719,19 +721,17 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D13" t="n">
-        <v>1824</v>
+        <v>1315</v>
       </c>
       <c r="E13" t="n">
-        <v>1824</v>
+        <v>1343</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9792000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>3727</v>
+        <v>5905</v>
       </c>
       <c r="E14" t="n">
-        <v>3821</v>
+        <v>5932</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9754</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1136</v>
+        <v>410</v>
       </c>
       <c r="E3" t="n">
-        <v>1136</v>
+        <v>410</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -533,10 +533,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1802</v>
+        <v>619</v>
       </c>
       <c r="E4" t="n">
-        <v>1802</v>
+        <v>619</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -545,7 +545,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +579,19 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>984</v>
+        <v>96</v>
       </c>
       <c r="E6" t="n">
-        <v>986</v>
+        <v>98</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.998</v>
+        <v>0.9795999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.971</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,13 +646,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>998</v>
+        <v>526</v>
       </c>
       <c r="E10" t="n">
-        <v>1015</v>
+        <v>533</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9833</v>
+        <v>0.9869</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -694,22 +694,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1315</v>
+        <v>288</v>
       </c>
       <c r="E13" t="n">
-        <v>1343</v>
+        <v>289</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9792000000000001</v>
+        <v>0.9965000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>239</v>
       </c>
       <c r="D14" t="n">
-        <v>5905</v>
+        <v>1956</v>
       </c>
       <c r="E14" t="n">
-        <v>5932</v>
+        <v>2195</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>410</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -533,19 +531,17 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>619</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +572,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9795999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +638,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +660,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>533</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -694,22 +682,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.8438</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +726,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>289</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9965000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1956</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2195</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.8911</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,20 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2444</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9767</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3774</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>3776</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9995000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2703</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>2704</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>186</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.7581</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2387</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>2388</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +697,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>258</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -729,17 +743,19 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>2781</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>2781</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>11107</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>11392</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.975</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2387</v>
+        <v>1223</v>
       </c>
       <c r="E3" t="n">
-        <v>2444</v>
+        <v>1227</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9767</v>
+        <v>0.9967</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>3774</v>
+        <v>2814</v>
       </c>
       <c r="E4" t="n">
-        <v>3776</v>
+        <v>2816</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>2703</v>
+        <v>2048</v>
       </c>
       <c r="E6" t="n">
-        <v>2704</v>
+        <v>2057</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9956</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
-        <v>141</v>
+        <v>441</v>
       </c>
       <c r="E8" t="n">
-        <v>186</v>
+        <v>510</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7581</v>
+        <v>0.8647</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +668,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>2387</v>
+        <v>1321</v>
       </c>
       <c r="E10" t="n">
-        <v>2388</v>
+        <v>1343</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.9836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="E11" t="n">
-        <v>258</v>
+        <v>140</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +729,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +738,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2781</v>
+        <v>2109</v>
       </c>
       <c r="E13" t="n">
-        <v>2781</v>
+        <v>2112</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +762,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>285</v>
+        <v>141</v>
       </c>
       <c r="D14" t="n">
-        <v>11107</v>
+        <v>7704</v>
       </c>
       <c r="E14" t="n">
-        <v>11392</v>
+        <v>7845</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.975</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1223</v>
+        <v>1184</v>
       </c>
       <c r="E3" t="n">
-        <v>1227</v>
+        <v>1184</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9967</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2814</v>
+        <v>1680</v>
       </c>
       <c r="E4" t="n">
-        <v>2816</v>
+        <v>1680</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>2048</v>
+        <v>1611</v>
       </c>
       <c r="E6" t="n">
-        <v>2057</v>
+        <v>1627</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9956</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>319</v>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>463</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8647</v>
+        <v>0.6890000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,22 +668,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>1321</v>
+        <v>955</v>
       </c>
       <c r="E10" t="n">
-        <v>1343</v>
+        <v>975</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9836</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="E11" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -707,7 +707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -738,22 +738,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2109</v>
+        <v>1387</v>
       </c>
       <c r="E13" t="n">
-        <v>2112</v>
+        <v>1387</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9986</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -762,22 +762,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>7704</v>
+        <v>6773</v>
       </c>
       <c r="E14" t="n">
-        <v>7845</v>
+        <v>6813</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.982</v>
+        <v>0.9941</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1184</v>
+        <v>1088</v>
       </c>
       <c r="E3" t="n">
-        <v>1184</v>
+        <v>1088</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>1680</v>
+        <v>1789</v>
       </c>
       <c r="E4" t="n">
-        <v>1680</v>
+        <v>1823</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
         <v>1611</v>
       </c>
       <c r="E6" t="n">
-        <v>1627</v>
+        <v>1641</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9902</v>
+        <v>0.9817</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="E8" t="n">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6890000000000001</v>
+        <v>0.7209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,20 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
-        <v>955</v>
+        <v>1515</v>
       </c>
       <c r="E10" t="n">
-        <v>975</v>
+        <v>1543</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9795</v>
+        <v>0.9819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -692,22 +694,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="E11" t="n">
-        <v>126</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0.9945000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -729,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -738,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>1387</v>
+        <v>1359</v>
       </c>
       <c r="E13" t="n">
-        <v>1387</v>
+        <v>1401</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -762,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>6773</v>
+        <v>5787</v>
       </c>
       <c r="E14" t="n">
-        <v>6813</v>
+        <v>5808</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9941</v>
+        <v>0.9964</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="E8" t="n">
         <v>412</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7209</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -670,16 +670,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="E10" t="n">
         <v>1543</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9819</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>5787</v>
+        <v>5806</v>
       </c>
       <c r="E14" t="n">
         <v>5808</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9964</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="15">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1088</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1088</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1789</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1823</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9813</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +572,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1611</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1641</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9817</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>412</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.9320000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,19 +641,17 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +660,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>1543</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.9843999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -694,22 +682,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>183</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.9945000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +726,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1359</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1401</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.97</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5806</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>5808</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$15</definedName>
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>356</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -531,17 +533,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>527</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>527</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>442</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>443</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9976999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>382</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>501</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.992</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +699,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -726,20 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>535</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>538</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9944</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1202</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>1471</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.8170999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2071</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2071</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4319</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>4493</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9612999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>4176</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9784</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -597,17 +603,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1065</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>1135</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9383</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2884</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>2950</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9776</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +699,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>337</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>337</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -726,20 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3814</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>3836</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9943000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>10397</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>10893</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9545</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D4" t="n">
         <v>4319</v>
       </c>
       <c r="E4" t="n">
-        <v>4493</v>
+        <v>4492</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9612999999999999</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="5">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D14" t="n">
         <v>10397</v>
       </c>
       <c r="E14" t="n">
-        <v>10893</v>
+        <v>10897</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9545</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>2071</v>
+        <v>1386</v>
       </c>
       <c r="E3" t="n">
-        <v>2071</v>
+        <v>1443</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9605</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>173</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4319</v>
+        <v>4503</v>
       </c>
       <c r="E4" t="n">
-        <v>4492</v>
+        <v>4506</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9615</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>4086</v>
+        <v>2762</v>
       </c>
       <c r="E6" t="n">
-        <v>4176</v>
+        <v>2786</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9784</v>
+        <v>0.9914000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D8" t="n">
-        <v>1065</v>
+        <v>1493</v>
       </c>
       <c r="E8" t="n">
-        <v>1135</v>
+        <v>1519</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9383</v>
+        <v>0.9829000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2884</v>
+        <v>2221</v>
       </c>
       <c r="E10" t="n">
-        <v>2950</v>
+        <v>2223</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9776</v>
+        <v>0.9991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>337</v>
+        <v>1012</v>
       </c>
       <c r="E11" t="n">
-        <v>337</v>
+        <v>1043</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3814</v>
+        <v>2212</v>
       </c>
       <c r="E13" t="n">
-        <v>3836</v>
+        <v>2215</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>500</v>
+        <v>295</v>
       </c>
       <c r="D14" t="n">
-        <v>10397</v>
+        <v>6647</v>
       </c>
       <c r="E14" t="n">
-        <v>10897</v>
+        <v>6942</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9575</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1386</v>
+        <v>1278</v>
       </c>
       <c r="E3" t="n">
-        <v>1443</v>
+        <v>1278</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9605</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="D4" t="n">
-        <v>4503</v>
+        <v>2414</v>
       </c>
       <c r="E4" t="n">
-        <v>4506</v>
+        <v>2482</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9993000000000001</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2762</v>
+        <v>2479</v>
       </c>
       <c r="E6" t="n">
-        <v>2786</v>
+        <v>2479</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9914000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="D7" t="n">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="E7" t="n">
-        <v>91</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n">
-        <v>1493</v>
+        <v>2033</v>
       </c>
       <c r="E8" t="n">
-        <v>1519</v>
+        <v>2126</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9829000000000001</v>
+        <v>0.9562999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>2221</v>
+        <v>2273</v>
       </c>
       <c r="E10" t="n">
-        <v>2223</v>
+        <v>2279</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9991</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1012</v>
+        <v>548</v>
       </c>
       <c r="E11" t="n">
-        <v>1043</v>
+        <v>548</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9703000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2212</v>
+        <v>1630</v>
       </c>
       <c r="E13" t="n">
-        <v>2215</v>
+        <v>1631</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9986</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="D14" t="n">
-        <v>6647</v>
+        <v>5985</v>
       </c>
       <c r="E14" t="n">
-        <v>6942</v>
+        <v>6132</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9575</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D3" t="n">
-        <v>1278</v>
+        <v>1342</v>
       </c>
       <c r="E3" t="n">
-        <v>1278</v>
+        <v>1383</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>2414</v>
+        <v>2707</v>
       </c>
       <c r="E4" t="n">
-        <v>2482</v>
+        <v>2784</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9726</v>
+        <v>0.9723000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>2479</v>
+        <v>2797</v>
       </c>
       <c r="E6" t="n">
-        <v>2479</v>
+        <v>2810</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="E7" t="n">
-        <v>405</v>
+        <v>101</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.479</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D8" t="n">
-        <v>2033</v>
+        <v>303</v>
       </c>
       <c r="E8" t="n">
-        <v>2126</v>
+        <v>374</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9562999999999999</v>
+        <v>0.8101999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>2273</v>
+        <v>1417</v>
       </c>
       <c r="E10" t="n">
-        <v>2279</v>
+        <v>1434</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9881</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>548</v>
+        <v>91</v>
       </c>
       <c r="E11" t="n">
-        <v>548</v>
+        <v>91</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1564</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1564</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1630</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1631</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="D14" t="n">
-        <v>5985</v>
+        <v>5466</v>
       </c>
       <c r="E14" t="n">
-        <v>6132</v>
+        <v>5588</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.976</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14" t="n">
-        <v>5466</v>
+        <v>5467</v>
       </c>
       <c r="E14" t="n">
         <v>5588</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9782</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1342</v>
+        <v>995</v>
       </c>
       <c r="E3" t="n">
-        <v>1383</v>
+        <v>995</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9704</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2707</v>
+        <v>4516</v>
       </c>
       <c r="E4" t="n">
-        <v>2784</v>
+        <v>4518</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9995999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="D6" t="n">
-        <v>2797</v>
+        <v>3148</v>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>3245</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9701000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
+        <v>424</v>
       </c>
       <c r="E8" t="n">
-        <v>374</v>
+        <v>441</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8101999999999999</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>1417</v>
+        <v>1183</v>
       </c>
       <c r="E10" t="n">
-        <v>1434</v>
+        <v>1191</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9881</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1564</v>
+        <v>1476</v>
       </c>
       <c r="E13" t="n">
-        <v>1564</v>
+        <v>1480</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>121</v>
+        <v>358</v>
       </c>
       <c r="D14" t="n">
-        <v>5467</v>
+        <v>4730</v>
       </c>
       <c r="E14" t="n">
-        <v>5588</v>
+        <v>5088</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n">
-        <v>3148</v>
+        <v>3150</v>
       </c>
       <c r="E6" t="n">
         <v>3245</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9701000000000001</v>
+        <v>0.9706999999999999</v>
       </c>
     </row>
     <row r="7">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>995</v>
+        <v>96</v>
       </c>
       <c r="E3" t="n">
-        <v>995</v>
+        <v>100</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>4516</v>
+        <v>435</v>
       </c>
       <c r="E4" t="n">
-        <v>4518</v>
+        <v>484</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>0.8987999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3150</v>
+        <v>1699</v>
       </c>
       <c r="E6" t="n">
-        <v>3245</v>
+        <v>1699</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9706999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
-        <v>183</v>
+        <v>33</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>441</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9615</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>0.4615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1183</v>
+        <v>323</v>
       </c>
       <c r="E10" t="n">
-        <v>1191</v>
+        <v>323</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9933</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.9274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>1476</v>
+        <v>311</v>
       </c>
       <c r="E13" t="n">
-        <v>1480</v>
+        <v>321</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.9688</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D14" t="n">
-        <v>4730</v>
+        <v>1740</v>
       </c>
       <c r="E14" t="n">
-        <v>5088</v>
+        <v>2092</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9296</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.96</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>484</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.8987999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1699</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1699</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,19 +597,17 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.09089999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +638,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.4615</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -675,19 +663,17 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>323</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,19 +685,17 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +726,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>311</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>321</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9688</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1740</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2092</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.8317</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,20 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>659</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>659</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>254</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -629,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,7 +659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +668,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,7 +705,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +727,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -739,7 +749,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +758,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1022</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>1022</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3611</v>
       </c>
       <c r="E3" t="n">
-        <v>659</v>
+        <v>3611</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>7890</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>7907</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>254</v>
+        <v>897</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5638</v>
       </c>
       <c r="E6" t="n">
-        <v>254</v>
+        <v>6535</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>0.8626999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>509</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,20 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1063</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>1405</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.2434</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,17 +651,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>3330</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -695,17 +699,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>266</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,20 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4617</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>4619</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9995999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -758,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1022</v>
+        <v>1595</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>14451</v>
       </c>
       <c r="E14" t="n">
-        <v>1022</v>
+        <v>16046</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>0.9006000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>7890</v>
+        <v>7892</v>
       </c>
       <c r="E4" t="n">
         <v>7907</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.9981</v>
       </c>
     </row>
     <row r="5">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="D14" t="n">
-        <v>14451</v>
+        <v>14454</v>
       </c>
       <c r="E14" t="n">
         <v>16046</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9006000000000001</v>
+        <v>0.9007999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3611</v>
+        <v>1322</v>
       </c>
       <c r="E3" t="n">
-        <v>3611</v>
+        <v>1322</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="D4" t="n">
-        <v>7892</v>
+        <v>7810</v>
       </c>
       <c r="E4" t="n">
-        <v>7907</v>
+        <v>7915</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9981</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>897</v>
+        <v>174</v>
       </c>
       <c r="D6" t="n">
-        <v>5638</v>
+        <v>5226</v>
       </c>
       <c r="E6" t="n">
-        <v>6535</v>
+        <v>5400</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8626999999999999</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>396</v>
+        <v>116</v>
       </c>
       <c r="E7" t="n">
-        <v>509</v>
+        <v>116</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1063</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>555</v>
       </c>
       <c r="E8" t="n">
-        <v>1405</v>
+        <v>610</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.2434</v>
+        <v>0.9098000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>3330</v>
+        <v>2364</v>
       </c>
       <c r="E10" t="n">
-        <v>3330</v>
+        <v>2364</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="E11" t="n">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>4617</v>
+        <v>2602</v>
       </c>
       <c r="E13" t="n">
-        <v>4619</v>
+        <v>2602</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9995999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1592</v>
+        <v>214</v>
       </c>
       <c r="D14" t="n">
-        <v>14454</v>
+        <v>8310</v>
       </c>
       <c r="E14" t="n">
-        <v>16046</v>
+        <v>8524</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9007999999999999</v>
+        <v>0.9749</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D4" t="n">
-        <v>7810</v>
+        <v>7812</v>
       </c>
       <c r="E4" t="n">
         <v>7915</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9867</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="5">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1322</v>
+        <v>1623</v>
       </c>
       <c r="E3" t="n">
-        <v>1322</v>
+        <v>1623</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>7812</v>
+        <v>5955</v>
       </c>
       <c r="E4" t="n">
-        <v>7915</v>
+        <v>6017</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.987</v>
+        <v>0.9897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>174</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>5226</v>
+        <v>4284</v>
       </c>
       <c r="E6" t="n">
-        <v>5400</v>
+        <v>4313</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9678</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="E7" t="n">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,19 +627,19 @@
         <v>55</v>
       </c>
       <c r="D8" t="n">
-        <v>555</v>
+        <v>328</v>
       </c>
       <c r="E8" t="n">
-        <v>610</v>
+        <v>383</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8564000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -675,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2364</v>
+        <v>1851</v>
       </c>
       <c r="E10" t="n">
-        <v>2364</v>
+        <v>1851</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>2602</v>
+        <v>2420</v>
       </c>
       <c r="E13" t="n">
-        <v>2602</v>
+        <v>2428</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9967</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>214</v>
+        <v>336</v>
       </c>
       <c r="D14" t="n">
-        <v>8310</v>
+        <v>5588</v>
       </c>
       <c r="E14" t="n">
-        <v>8524</v>
+        <v>5924</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9749</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>4284</v>
+        <v>4285</v>
       </c>
       <c r="E6" t="n">
         <v>4313</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9933</v>
+        <v>0.9934999999999999</v>
       </c>
     </row>
     <row r="7">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1623</v>
+        <v>915</v>
       </c>
       <c r="E3" t="n">
-        <v>1623</v>
+        <v>916</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5955</v>
+        <v>2676</v>
       </c>
       <c r="E4" t="n">
-        <v>6017</v>
+        <v>2696</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9897</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>4285</v>
+        <v>2157</v>
       </c>
       <c r="E6" t="n">
-        <v>4313</v>
+        <v>2172</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9934999999999999</v>
+        <v>0.9931</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E7" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>446</v>
       </c>
       <c r="E8" t="n">
-        <v>383</v>
+        <v>491</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.9084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>1851</v>
+        <v>1445</v>
       </c>
       <c r="E10" t="n">
-        <v>1851</v>
+        <v>1596</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0.9054000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>2420</v>
+        <v>1984</v>
       </c>
       <c r="E13" t="n">
-        <v>2428</v>
+        <v>2055</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9967</v>
+        <v>0.9655</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>336</v>
+        <v>157</v>
       </c>
       <c r="D14" t="n">
-        <v>5588</v>
+        <v>5241</v>
       </c>
       <c r="E14" t="n">
-        <v>5924</v>
+        <v>5398</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9433</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>232</v>
+      </c>
+      <c r="E3" t="n">
+        <v>232</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>915</v>
-      </c>
-      <c r="E3" t="n">
-        <v>916</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.9989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D4" t="n">
-        <v>2676</v>
+        <v>271</v>
       </c>
       <c r="E4" t="n">
-        <v>2696</v>
+        <v>326</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9926</v>
+        <v>0.8312999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2157</v>
+        <v>279</v>
       </c>
       <c r="E6" t="n">
-        <v>2172</v>
+        <v>279</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9931</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>491</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9084</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1445</v>
+        <v>356</v>
       </c>
       <c r="E10" t="n">
-        <v>1596</v>
+        <v>356</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9054000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>1984</v>
+        <v>431</v>
       </c>
       <c r="E13" t="n">
-        <v>2055</v>
+        <v>510</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9655</v>
+        <v>0.8451000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>5241</v>
+        <v>1334</v>
       </c>
       <c r="E14" t="n">
-        <v>5398</v>
+        <v>1418</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9709</v>
+        <v>0.9408</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>232</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>271</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>326</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.8312999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>279</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,19 +597,17 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,19 +641,17 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -675,19 +663,17 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>356</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,19 +685,17 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +726,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.8451000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1334</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1418</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9408</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1669</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>1669</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>787</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4341</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>5128</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.8465</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3385</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>3711</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9122</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -597,17 +603,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>338</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>338</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>661</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>808</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.8181</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -641,17 +651,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>155</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2722</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>2876</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.9465</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +699,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>116</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -726,20 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3628</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>3648</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9945000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>11516</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>11944</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9642000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D4" t="n">
-        <v>4341</v>
+        <v>4343</v>
       </c>
       <c r="E4" t="n">
         <v>5128</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8465</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="5">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D14" t="n">
-        <v>11516</v>
+        <v>11517</v>
       </c>
       <c r="E14" t="n">
         <v>11944</v>

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1669</v>
+        <v>1781</v>
       </c>
       <c r="E3" t="n">
-        <v>1669</v>
+        <v>1783</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>785</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>4343</v>
+        <v>5572</v>
       </c>
       <c r="E4" t="n">
-        <v>5128</v>
+        <v>5590</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8469</v>
+        <v>0.9968</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>326</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>3385</v>
+        <v>2945</v>
       </c>
       <c r="E6" t="n">
-        <v>3711</v>
+        <v>2967</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9122</v>
+        <v>0.9926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>338</v>
+        <v>215</v>
       </c>
       <c r="E7" t="n">
-        <v>338</v>
+        <v>215</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>147</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>661</v>
+        <v>436</v>
       </c>
       <c r="E8" t="n">
-        <v>808</v>
+        <v>487</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8181</v>
+        <v>0.8953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="E9" t="n">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>2722</v>
+        <v>1891</v>
       </c>
       <c r="E10" t="n">
-        <v>2876</v>
+        <v>1912</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9465</v>
+        <v>0.9890000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>332</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3628</v>
+        <v>3069</v>
       </c>
       <c r="E13" t="n">
-        <v>3648</v>
+        <v>3070</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9945000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>427</v>
+        <v>211</v>
       </c>
       <c r="D14" t="n">
-        <v>11517</v>
+        <v>7359</v>
       </c>
       <c r="E14" t="n">
-        <v>11944</v>
+        <v>7570</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9642000000000001</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1781</v>
+        <v>1129</v>
       </c>
       <c r="E3" t="n">
-        <v>1783</v>
+        <v>1129</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9989</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>5572</v>
+        <v>2750</v>
       </c>
       <c r="E4" t="n">
-        <v>5590</v>
+        <v>2786</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9968</v>
+        <v>0.9871</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>2945</v>
+        <v>1806</v>
       </c>
       <c r="E6" t="n">
-        <v>2967</v>
+        <v>1835</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9926</v>
+        <v>0.9842</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>507</v>
       </c>
       <c r="E8" t="n">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8953</v>
+        <v>0.9864000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E9" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="D10" t="n">
-        <v>1891</v>
+        <v>1135</v>
       </c>
       <c r="E10" t="n">
-        <v>1912</v>
+        <v>1499</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.7572</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="E11" t="n">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +742,22 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2187</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2187</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3069</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3070</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9997</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>211</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>7359</v>
+        <v>6287</v>
       </c>
       <c r="E14" t="n">
-        <v>7570</v>
+        <v>6303</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9721</v>
+        <v>0.9975000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1129</v>
+        <v>1554</v>
       </c>
       <c r="E3" t="n">
-        <v>1129</v>
+        <v>1554</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D4" t="n">
-        <v>2750</v>
+        <v>2562</v>
       </c>
       <c r="E4" t="n">
-        <v>2786</v>
+        <v>2604</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9871</v>
+        <v>0.9839</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>1806</v>
+        <v>1583</v>
       </c>
       <c r="E6" t="n">
-        <v>1835</v>
+        <v>1610</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9842</v>
+        <v>0.9832</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>507</v>
+        <v>462</v>
       </c>
       <c r="E8" t="n">
-        <v>514</v>
+        <v>483</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1135</v>
+        <v>1427</v>
       </c>
       <c r="E10" t="n">
-        <v>1499</v>
+        <v>1428</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.7572</v>
+        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="E11" t="n">
-        <v>115</v>
+        <v>196</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2187</v>
+        <v>1955</v>
       </c>
       <c r="E13" t="n">
-        <v>2187</v>
+        <v>1955</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -757,7 +757,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>198</v>
       </c>
       <c r="D14" t="n">
-        <v>6287</v>
+        <v>7114</v>
       </c>
       <c r="E14" t="n">
-        <v>6303</v>
+        <v>7312</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.9729000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1554</v>
+        <v>1366</v>
       </c>
       <c r="E3" t="n">
-        <v>1554</v>
+        <v>1366</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>2562</v>
+        <v>2214</v>
       </c>
       <c r="E4" t="n">
-        <v>2604</v>
+        <v>2313</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9839</v>
+        <v>0.9571999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>1583</v>
+        <v>1764</v>
       </c>
       <c r="E6" t="n">
-        <v>1610</v>
+        <v>1810</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9832</v>
+        <v>0.9745999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -615,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>336</v>
       </c>
       <c r="E8" t="n">
-        <v>483</v>
+        <v>392</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9565</v>
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +651,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>145</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -672,22 +672,22 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1783</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1783</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1427</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1428</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.9993000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1955</v>
+        <v>1835</v>
       </c>
       <c r="E13" t="n">
-        <v>1955</v>
+        <v>1835</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -757,7 +757,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +766,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>198</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>7114</v>
+        <v>7504</v>
       </c>
       <c r="E14" t="n">
-        <v>7312</v>
+        <v>7542</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1366</v>
+        <v>378</v>
       </c>
       <c r="E3" t="n">
-        <v>1366</v>
+        <v>378</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="D4" t="n">
-        <v>2214</v>
+        <v>614</v>
       </c>
       <c r="E4" t="n">
-        <v>2313</v>
+        <v>676</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9571999999999999</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1764</v>
+        <v>141</v>
       </c>
       <c r="E6" t="n">
-        <v>1810</v>
+        <v>141</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9745999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -603,19 +603,17 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>392</v>
+        <v>37</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -651,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
-        <v>145</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -663,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -675,10 +673,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1783</v>
+        <v>616</v>
       </c>
       <c r="E10" t="n">
-        <v>1783</v>
+        <v>616</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -687,7 +685,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -699,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -711,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -733,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1835</v>
+        <v>442</v>
       </c>
       <c r="E13" t="n">
-        <v>1835</v>
+        <v>445</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9933</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -766,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="D14" t="n">
-        <v>7504</v>
+        <v>2553</v>
       </c>
       <c r="E14" t="n">
-        <v>7542</v>
+        <v>2702</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.995</v>
+        <v>0.9449</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,17 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>378</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>676</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9083</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>141</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,19 +641,17 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -673,19 +663,17 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>616</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>616</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,19 +685,17 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +726,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>445</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.9933</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2553</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2702</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9449</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,20 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2798</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>2812</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.995</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4432</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>4714</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9401999999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>5863</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>5994</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9781</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>687</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.444</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -641,17 +649,19 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>351</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -660,20 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>615</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3345</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>3960</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.8447</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +697,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -726,20 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3775</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>3808</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.9913</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>13972</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>14480</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9649</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2798</v>
+        <v>1637</v>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1637</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>282</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>4432</v>
+        <v>4384</v>
       </c>
       <c r="E4" t="n">
-        <v>4714</v>
+        <v>4480</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.9786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>131</v>
+        <v>339</v>
       </c>
       <c r="D6" t="n">
-        <v>5863</v>
+        <v>5757</v>
       </c>
       <c r="E6" t="n">
-        <v>5994</v>
+        <v>6096</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9781</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>305</v>
+        <v>637</v>
       </c>
       <c r="E8" t="n">
-        <v>687</v>
+        <v>651</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.444</v>
+        <v>0.9784999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="E9" t="n">
-        <v>351</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>615</v>
+        <v>109</v>
       </c>
       <c r="D10" t="n">
-        <v>3345</v>
+        <v>2951</v>
       </c>
       <c r="E10" t="n">
-        <v>3960</v>
+        <v>3060</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.8447</v>
+        <v>0.9643999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3775</v>
+        <v>2894</v>
       </c>
       <c r="E13" t="n">
-        <v>3808</v>
+        <v>2894</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9913</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>508</v>
+        <v>303</v>
       </c>
       <c r="D14" t="n">
-        <v>13972</v>
+        <v>10448</v>
       </c>
       <c r="E14" t="n">
-        <v>14480</v>
+        <v>10751</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9649</v>
+        <v>0.9718000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,10 +509,10 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1637</v>
+        <v>1594</v>
       </c>
       <c r="E3" t="n">
-        <v>1637</v>
+        <v>1594</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>4384</v>
+        <v>2209</v>
       </c>
       <c r="E4" t="n">
-        <v>4480</v>
+        <v>2269</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9786</v>
+        <v>0.9736</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>5757</v>
+        <v>2208</v>
       </c>
       <c r="E6" t="n">
-        <v>6096</v>
+        <v>2229</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9444</v>
+        <v>0.9906</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>637</v>
+        <v>351</v>
       </c>
       <c r="E8" t="n">
-        <v>651</v>
+        <v>355</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9784999999999999</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
+        <v>0.9734999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2951</v>
+        <v>1562</v>
       </c>
       <c r="E10" t="n">
-        <v>3060</v>
+        <v>1562</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9643999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2894</v>
+        <v>2416</v>
       </c>
       <c r="E13" t="n">
-        <v>2894</v>
+        <v>2416</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>303</v>
+        <v>134</v>
       </c>
       <c r="D14" t="n">
-        <v>10448</v>
+        <v>7040</v>
       </c>
       <c r="E14" t="n">
-        <v>10751</v>
+        <v>7174</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9718000000000001</v>
+        <v>0.9813</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1594</v>
+        <v>1308</v>
       </c>
       <c r="E3" t="n">
-        <v>1594</v>
+        <v>1312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>2209</v>
+        <v>2091</v>
       </c>
       <c r="E4" t="n">
-        <v>2269</v>
+        <v>2103</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9736</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>2208</v>
+        <v>1835</v>
       </c>
       <c r="E6" t="n">
-        <v>2229</v>
+        <v>1864</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9906</v>
+        <v>0.9843999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
         <v>351</v>
       </c>
       <c r="E8" t="n">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9887</v>
+        <v>0.9213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>320</v>
       </c>
       <c r="E9" t="n">
-        <v>189</v>
+        <v>320</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9734999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>1562</v>
+        <v>2287</v>
       </c>
       <c r="E10" t="n">
-        <v>1562</v>
+        <v>2329</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -743,10 +743,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2416</v>
+        <v>1798</v>
       </c>
       <c r="E13" t="n">
-        <v>2416</v>
+        <v>1798</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>134</v>
+        <v>676</v>
       </c>
       <c r="D14" t="n">
-        <v>7040</v>
+        <v>6846</v>
       </c>
       <c r="E14" t="n">
-        <v>7174</v>
+        <v>7522</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9813</v>
+        <v>0.9101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1308</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.997</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +528,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2091</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2103</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9943000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +572,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1835</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1864</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9843999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +616,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>381</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.9213</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,19 +641,17 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>320</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +660,20 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2287</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2329</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.982</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,19 +685,17 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +717,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -743,19 +729,17 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1798</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1798</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +748,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>6846</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>7522</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9101</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,20 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3577</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="n"/>
+        <v>3602</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.9931</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -528,20 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4598</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n"/>
+        <v>4760</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.966</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>4221</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9751000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -607,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>926</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.9179</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>378</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9974</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,17 +673,19 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3558</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>3558</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -685,17 +697,19 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
+        <v>194</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -717,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -729,17 +743,19 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>3754</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="n"/>
+        <v>3754</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -748,20 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>11774</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="n"/>
+        <v>12554</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.9379000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>3577</v>
+        <v>1888</v>
       </c>
       <c r="E3" t="n">
-        <v>3602</v>
+        <v>1910</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9931</v>
+        <v>0.9884999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>162</v>
+        <v>353</v>
       </c>
       <c r="D4" t="n">
-        <v>4598</v>
+        <v>3681</v>
       </c>
       <c r="E4" t="n">
-        <v>4760</v>
+        <v>4034</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.966</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
-        <v>4116</v>
+        <v>2209</v>
       </c>
       <c r="E6" t="n">
-        <v>4221</v>
+        <v>2286</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9751000000000001</v>
+        <v>0.9662999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>76</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>850</v>
+        <v>577</v>
       </c>
       <c r="E8" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9179</v>
+        <v>0.6224000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,19 +649,19 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>217</v>
       </c>
       <c r="E9" t="n">
-        <v>378</v>
+        <v>218</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9974</v>
+        <v>0.9954000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>3558</v>
+        <v>3349</v>
       </c>
       <c r="E10" t="n">
-        <v>3558</v>
+        <v>3351</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>194</v>
+        <v>62</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3754</v>
+        <v>1940</v>
       </c>
       <c r="E13" t="n">
-        <v>3754</v>
+        <v>1941</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>780</v>
+        <v>203</v>
       </c>
       <c r="D14" t="n">
-        <v>11774</v>
+        <v>9476</v>
       </c>
       <c r="E14" t="n">
-        <v>12554</v>
+        <v>9679</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9379000000000001</v>
+        <v>0.9790000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1888</v>
+        <v>1783</v>
       </c>
       <c r="E3" t="n">
-        <v>1910</v>
+        <v>1783</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9884999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>353</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>3681</v>
+        <v>2775</v>
       </c>
       <c r="E4" t="n">
-        <v>4034</v>
+        <v>2802</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9125</v>
+        <v>0.9904000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>2209</v>
+        <v>2466</v>
       </c>
       <c r="E6" t="n">
-        <v>2286</v>
+        <v>2501</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9662999999999999</v>
+        <v>0.986</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
-        <v>577</v>
+        <v>2157</v>
       </c>
       <c r="E8" t="n">
-        <v>927</v>
+        <v>2281</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6224000000000001</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="E9" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9954000000000001</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>3349</v>
+        <v>2245</v>
       </c>
       <c r="E10" t="n">
-        <v>3351</v>
+        <v>2258</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9994</v>
+        <v>0.9942</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>1940</v>
+        <v>1776</v>
       </c>
       <c r="E13" t="n">
-        <v>1941</v>
+        <v>1779</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9983</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="D14" t="n">
-        <v>9476</v>
+        <v>8775</v>
       </c>
       <c r="E14" t="n">
-        <v>9679</v>
+        <v>8896</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9790000000000001</v>
+        <v>0.9864000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1783</v>
+        <v>1992</v>
       </c>
       <c r="E3" t="n">
-        <v>1783</v>
+        <v>1994</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1</v>
+        <v>0.9990000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="D4" t="n">
-        <v>2775</v>
+        <v>2546</v>
       </c>
       <c r="E4" t="n">
-        <v>2802</v>
+        <v>2838</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9904000000000001</v>
+        <v>0.8970999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
-        <v>2466</v>
+        <v>2445</v>
       </c>
       <c r="E6" t="n">
-        <v>2501</v>
+        <v>2459</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.986</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>2157</v>
+        <v>790</v>
       </c>
       <c r="E8" t="n">
-        <v>2281</v>
+        <v>890</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9456</v>
+        <v>0.8876000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>132</v>
+        <v>315</v>
       </c>
       <c r="E9" t="n">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9778</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2245</v>
+        <v>2674</v>
       </c>
       <c r="E10" t="n">
-        <v>2258</v>
+        <v>2674</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.9942</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1776</v>
+        <v>1929</v>
       </c>
       <c r="E13" t="n">
-        <v>1779</v>
+        <v>1934</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9983</v>
+        <v>0.9974</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>121</v>
+        <v>613</v>
       </c>
       <c r="D14" t="n">
-        <v>8775</v>
+        <v>8288</v>
       </c>
       <c r="E14" t="n">
-        <v>8896</v>
+        <v>8901</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -506,22 +506,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>1992</v>
+        <v>866</v>
       </c>
       <c r="E3" t="n">
-        <v>1994</v>
+        <v>887</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.9990000000000001</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>292</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>2546</v>
+        <v>530</v>
       </c>
       <c r="E4" t="n">
-        <v>2838</v>
+        <v>536</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8970999999999999</v>
+        <v>0.9887999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>2445</v>
+        <v>461</v>
       </c>
       <c r="E6" t="n">
-        <v>2459</v>
+        <v>492</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.9370000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>890</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.8876000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -649,10 +649,10 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="E9" t="n">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -661,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -673,10 +673,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>2674</v>
+        <v>833</v>
       </c>
       <c r="E10" t="n">
-        <v>2674</v>
+        <v>833</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -685,7 +685,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
@@ -709,7 +709,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,22 +740,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1929</v>
+        <v>611</v>
       </c>
       <c r="E13" t="n">
-        <v>1934</v>
+        <v>611</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.9974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>613</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>8288</v>
+        <v>2957</v>
       </c>
       <c r="E14" t="n">
-        <v>8901</v>
+        <v>3038</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.9311</v>
+        <v>0.9732999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -475,12 +475,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CARAP 02-SP</t>
+          <t>CHM-SP</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -497,60 +497,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CARAP-SP</t>
+          <t>CLP-SP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>866</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>887</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.9762999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHM-SP</t>
+          <t>F JND-SP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>536</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9887999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CLP-SP</t>
+          <t>F S-JRG-SP</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -567,36 +563,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COT-SP</t>
+          <t>ITUP-SP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9370000000000001</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F JND-SP</t>
+          <t>JND 02-SP</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -613,193 +607,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F S-JRG-SP</t>
+          <t>JND-SP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ITUP-SP</t>
+          <t>OSC 02-SP</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>91</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JND 02-SP</t>
+          <t>OSC-SP</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>833</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JND-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>OSC 02-SP</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>OSC-SP</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>611</v>
-      </c>
-      <c r="E13" t="n">
-        <v>611</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>S-CSVD-SP</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>81</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2957</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3038</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.9732999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Taxa de Coletas por Base" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Taxa de Coletas por Base'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,20 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>402</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>7370</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>7772</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9483</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,20 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10071</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>10183</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9890000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>772</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>852</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9061</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3893</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>4591</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.848</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,44 +627,48 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>85</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OSC 02-SP</t>
+          <t>S-CSVD-SP</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1708</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12579</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>14287</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8804999999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OSC-SP</t>
+          <t>S-FREG-SP</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -670,30 +682,8 @@
       </c>
       <c r="F10" s="2" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>S-FREG-SP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>402</v>
+        <v>643</v>
       </c>
       <c r="D2" t="n">
-        <v>7370</v>
+        <v>8583</v>
       </c>
       <c r="E2" t="n">
-        <v>7772</v>
+        <v>9226</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9483</v>
+        <v>0.9303</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>112</v>
+        <v>297</v>
       </c>
       <c r="D5" t="n">
-        <v>10071</v>
+        <v>359</v>
       </c>
       <c r="E5" t="n">
-        <v>10183</v>
+        <v>656</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9890000000000001</v>
+        <v>0.5473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>335</v>
       </c>
       <c r="E6" t="n">
-        <v>852</v>
+        <v>335</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9061</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>698</v>
+        <v>398</v>
       </c>
       <c r="D7" t="n">
-        <v>3893</v>
+        <v>3280</v>
       </c>
       <c r="E7" t="n">
-        <v>4591</v>
+        <v>3678</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.848</v>
+        <v>0.8918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1708</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>12579</v>
+        <v>9980</v>
       </c>
       <c r="E9" t="n">
-        <v>14287</v>
+        <v>10276</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.9712000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>643</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>8583</v>
+        <v>5714</v>
       </c>
       <c r="E2" t="n">
-        <v>9226</v>
+        <v>5771</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9303</v>
+        <v>0.9901000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>297</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>359</v>
+        <v>967</v>
       </c>
       <c r="E5" t="n">
-        <v>656</v>
+        <v>969</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5473</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="E6" t="n">
-        <v>335</v>
+        <v>418</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.7487999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>398</v>
+        <v>573</v>
       </c>
       <c r="D7" t="n">
-        <v>3280</v>
+        <v>2462</v>
       </c>
       <c r="E7" t="n">
-        <v>3678</v>
+        <v>3035</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8918</v>
+        <v>0.8112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>554</v>
       </c>
       <c r="D9" t="n">
-        <v>9980</v>
+        <v>7741</v>
       </c>
       <c r="E9" t="n">
-        <v>10276</v>
+        <v>8295</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9712000000000001</v>
+        <v>0.9331999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>5714</v>
+        <v>2763</v>
       </c>
       <c r="E2" t="n">
-        <v>5771</v>
+        <v>2825</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9901000000000001</v>
+        <v>0.9781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>967</v>
+        <v>901</v>
       </c>
       <c r="E5" t="n">
-        <v>969</v>
+        <v>1047</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9979</v>
+        <v>0.8606</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>313</v>
+        <v>484</v>
       </c>
       <c r="E6" t="n">
-        <v>418</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7487999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>573</v>
+        <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>2462</v>
+        <v>3090</v>
       </c>
       <c r="E7" t="n">
-        <v>3035</v>
+        <v>3158</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8112</v>
+        <v>0.9784999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="E8" t="n">
-        <v>78</v>
+        <v>152</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>960</v>
       </c>
       <c r="D9" t="n">
-        <v>7741</v>
+        <v>7165</v>
       </c>
       <c r="E9" t="n">
-        <v>8295</v>
+        <v>8125</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9331999999999999</v>
+        <v>0.8818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2763</v>
+        <v>700</v>
       </c>
       <c r="E2" t="n">
-        <v>2825</v>
+        <v>700</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9781</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>901</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>1047</v>
+        <v>37</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8606</v>
+        <v>0.2703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
-        <v>3090</v>
+        <v>710</v>
       </c>
       <c r="E7" t="n">
-        <v>3158</v>
+        <v>1027</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9784999999999999</v>
+        <v>0.6912999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E8" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>960</v>
+        <v>114</v>
       </c>
       <c r="D9" t="n">
-        <v>7165</v>
+        <v>2588</v>
       </c>
       <c r="E9" t="n">
-        <v>8125</v>
+        <v>2702</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8818</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,17 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>700</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +519,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +550,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.2703</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +594,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>710</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1027</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.6912999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,19 +619,17 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +638,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2588</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2702</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9578</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,20 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>145</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,20 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>92</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>239</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,20 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>1400</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.775</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>145</v>
+        <v>652</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8459</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>9111</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
+        <v>0.9284</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>611</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1763</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>0.6534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>1012</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
+        <v>0.8597</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>239</v>
+        <v>1086</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="E7" t="n">
-        <v>239</v>
+        <v>6686</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
+        <v>0.8376</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>359</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>3652</v>
       </c>
       <c r="D9" t="n">
-        <v>1085</v>
+        <v>17217</v>
       </c>
       <c r="E9" t="n">
-        <v>1400</v>
+        <v>20869</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.775</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>652</v>
+        <v>797</v>
       </c>
       <c r="D2" t="n">
-        <v>8459</v>
+        <v>7076</v>
       </c>
       <c r="E2" t="n">
-        <v>9111</v>
+        <v>7873</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9284</v>
+        <v>0.8987999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>611</v>
+        <v>116</v>
       </c>
       <c r="D5" t="n">
-        <v>1152</v>
+        <v>785</v>
       </c>
       <c r="E5" t="n">
-        <v>1763</v>
+        <v>901</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.6534</v>
+        <v>0.8713</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>993</v>
       </c>
       <c r="E6" t="n">
-        <v>1012</v>
+        <v>993</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8597</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1086</v>
+        <v>912</v>
       </c>
       <c r="D7" t="n">
-        <v>5600</v>
+        <v>3750</v>
       </c>
       <c r="E7" t="n">
-        <v>6686</v>
+        <v>4662</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8376</v>
+        <v>0.8044</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>275</v>
+      </c>
+      <c r="E8" t="n">
+        <v>275</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>358</v>
-      </c>
-      <c r="E8" t="n">
-        <v>359</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.9972</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3652</v>
+        <v>1258</v>
       </c>
       <c r="D9" t="n">
-        <v>17217</v>
+        <v>10896</v>
       </c>
       <c r="E9" t="n">
-        <v>20869</v>
+        <v>12154</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.825</v>
+        <v>0.8965000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>797</v>
+        <v>407</v>
       </c>
       <c r="D2" t="n">
-        <v>7076</v>
+        <v>3817</v>
       </c>
       <c r="E2" t="n">
-        <v>7873</v>
+        <v>4224</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8987999999999999</v>
+        <v>0.9036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D5" t="n">
-        <v>785</v>
+        <v>621</v>
       </c>
       <c r="E5" t="n">
-        <v>901</v>
+        <v>693</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8713</v>
+        <v>0.8961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>993</v>
+        <v>557</v>
       </c>
       <c r="E6" t="n">
-        <v>993</v>
+        <v>558</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>912</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3750</v>
+        <v>3140</v>
       </c>
       <c r="E7" t="n">
-        <v>4662</v>
+        <v>3142</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8044</v>
+        <v>0.9994</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>275</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>275</v>
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1258</v>
+        <v>398</v>
       </c>
       <c r="D9" t="n">
-        <v>10896</v>
+        <v>7098</v>
       </c>
       <c r="E9" t="n">
-        <v>12154</v>
+        <v>7496</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8965000000000001</v>
+        <v>0.9469</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>407</v>
+        <v>98</v>
       </c>
       <c r="D2" t="n">
-        <v>3817</v>
+        <v>3585</v>
       </c>
       <c r="E2" t="n">
-        <v>4224</v>
+        <v>3683</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9036</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>621</v>
+        <v>128</v>
       </c>
       <c r="E5" t="n">
-        <v>693</v>
+        <v>166</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8961</v>
+        <v>0.7711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>435</v>
+      </c>
+      <c r="E6" t="n">
+        <v>435</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>557</v>
-      </c>
-      <c r="E6" t="n">
-        <v>558</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>3140</v>
+        <v>2499</v>
       </c>
       <c r="E7" t="n">
-        <v>3142</v>
+        <v>2506</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9994</v>
+        <v>0.9972</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>398</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>7098</v>
+        <v>6783</v>
       </c>
       <c r="E9" t="n">
-        <v>7496</v>
+        <v>7134</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9469</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>98</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>3585</v>
+        <v>354</v>
       </c>
       <c r="E2" t="n">
-        <v>3683</v>
+        <v>366</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9734</v>
+        <v>0.9671999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7711</v>
+        <v>0.2778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,10 +579,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>435</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>435</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="D7" t="n">
-        <v>2499</v>
+        <v>356</v>
       </c>
       <c r="E7" t="n">
-        <v>2506</v>
+        <v>461</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9972</v>
+        <v>0.7722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>523</v>
       </c>
       <c r="D9" t="n">
-        <v>6783</v>
+        <v>2168</v>
       </c>
       <c r="E9" t="n">
-        <v>7134</v>
+        <v>2691</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9508</v>
+        <v>0.8056</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9671999999999999</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +519,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +550,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.2778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -579,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +594,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>461</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.7722</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,19 +619,17 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +638,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2168</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2691</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.8056</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,20 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5253</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>5331</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9854000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,20 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n"/>
+        <v>264</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9886</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,20 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>965</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.3482</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,20 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6514</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>6673</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.9762000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,17 +627,19 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>131</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2013</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10195</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>12208</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.8351000000000001</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D2" t="n">
-        <v>5253</v>
+        <v>2827</v>
       </c>
       <c r="E2" t="n">
-        <v>5331</v>
+        <v>2871</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>261</v>
+        <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>264</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9886</v>
+        <v>0.8029999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>629</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>336</v>
+        <v>828</v>
       </c>
       <c r="E6" t="n">
-        <v>965</v>
+        <v>828</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.3482</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6514</v>
+        <v>3753</v>
       </c>
       <c r="E7" t="n">
-        <v>6673</v>
+        <v>3753</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9762000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2013</v>
+        <v>1010</v>
       </c>
       <c r="D9" t="n">
-        <v>10195</v>
+        <v>7874</v>
       </c>
       <c r="E9" t="n">
-        <v>12208</v>
+        <v>8884</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8351000000000001</v>
+        <v>0.8863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>2827</v>
+        <v>3034</v>
       </c>
       <c r="E2" t="n">
-        <v>2871</v>
+        <v>3064</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9847</v>
+        <v>0.9902</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.8029999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>828</v>
+        <v>865</v>
       </c>
       <c r="E6" t="n">
-        <v>828</v>
+        <v>870</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.9943000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>3753</v>
+        <v>2834</v>
       </c>
       <c r="E7" t="n">
-        <v>3753</v>
+        <v>2839</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="E8" t="n">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +639,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1010</v>
+        <v>526</v>
       </c>
       <c r="D9" t="n">
-        <v>7874</v>
+        <v>7118</v>
       </c>
       <c r="E9" t="n">
-        <v>8884</v>
+        <v>7644</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8863</v>
+        <v>0.9312</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>3034</v>
+        <v>3285</v>
       </c>
       <c r="E2" t="n">
-        <v>3064</v>
+        <v>3348</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9902</v>
+        <v>0.9812000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -552,22 +552,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,22 +574,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>865</v>
+        <v>584</v>
       </c>
       <c r="E6" t="n">
-        <v>870</v>
+        <v>684</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9943000000000001</v>
+        <v>0.8538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,22 +598,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2834</v>
+        <v>3478</v>
       </c>
       <c r="E7" t="n">
-        <v>2839</v>
+        <v>3478</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.9982</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -627,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -639,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -648,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>526</v>
+        <v>976</v>
       </c>
       <c r="D9" t="n">
-        <v>7118</v>
+        <v>6195</v>
       </c>
       <c r="E9" t="n">
-        <v>7644</v>
+        <v>7171</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9312</v>
+        <v>0.8639</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D2" t="n">
-        <v>3285</v>
+        <v>2480</v>
       </c>
       <c r="E2" t="n">
-        <v>3348</v>
+        <v>2539</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9812000000000001</v>
+        <v>0.9768000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -574,22 +574,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>584</v>
+        <v>510</v>
       </c>
       <c r="E6" t="n">
-        <v>684</v>
+        <v>510</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.8538</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3478</v>
+        <v>3756</v>
       </c>
       <c r="E7" t="n">
-        <v>3478</v>
+        <v>3756</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>976</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>6195</v>
+        <v>6299</v>
       </c>
       <c r="E9" t="n">
-        <v>7171</v>
+        <v>6516</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8639</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2480</v>
+        <v>696</v>
       </c>
       <c r="E2" t="n">
-        <v>2539</v>
+        <v>696</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9768000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>510</v>
+        <v>222</v>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>222</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3756</v>
+        <v>389</v>
       </c>
       <c r="E7" t="n">
-        <v>3756</v>
+        <v>389</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>217</v>
+        <v>757</v>
       </c>
       <c r="D9" t="n">
-        <v>6299</v>
+        <v>1867</v>
       </c>
       <c r="E9" t="n">
-        <v>6516</v>
+        <v>2624</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9667</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,17 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>696</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>696</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +519,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,19 +575,17 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>222</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,19 +597,17 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>389</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,19 +619,17 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +638,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1867</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2624</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.7115</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,20 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4602</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n"/>
+        <v>4677</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.9840000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -575,17 +577,19 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
+        <v>1012</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -597,17 +601,19 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6479</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="n"/>
+        <v>6479</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,17 +625,19 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n"/>
+        <v>180</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -638,20 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>10698</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n"/>
+        <v>11556</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.9258</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4602</v>
+        <v>3284</v>
       </c>
       <c r="E2" t="n">
-        <v>4677</v>
+        <v>3290</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9840000000000001</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1012</v>
+        <v>570</v>
       </c>
       <c r="E6" t="n">
-        <v>1012</v>
+        <v>570</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>6479</v>
+        <v>3982</v>
       </c>
       <c r="E7" t="n">
-        <v>6479</v>
+        <v>3982</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="E8" t="n">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>858</v>
+        <v>407</v>
       </c>
       <c r="D9" t="n">
-        <v>10698</v>
+        <v>7106</v>
       </c>
       <c r="E9" t="n">
-        <v>11556</v>
+        <v>7513</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9258</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>3284</v>
+        <v>2178</v>
       </c>
       <c r="E2" t="n">
-        <v>3290</v>
+        <v>2184</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9982</v>
+        <v>0.9973000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>570</v>
+        <v>391</v>
       </c>
       <c r="E6" t="n">
-        <v>570</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -601,10 +601,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3982</v>
+        <v>3306</v>
       </c>
       <c r="E7" t="n">
-        <v>3982</v>
+        <v>3306</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
@@ -613,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>407</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>7106</v>
+        <v>5822</v>
       </c>
       <c r="E9" t="n">
-        <v>7513</v>
+        <v>6056</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9458</v>
+        <v>0.9614</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>372</v>
       </c>
       <c r="D2" t="n">
-        <v>2178</v>
+        <v>1459</v>
       </c>
       <c r="E2" t="n">
-        <v>2184</v>
+        <v>1831</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9973000000000001</v>
+        <v>0.7968000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>391</v>
+        <v>721</v>
       </c>
       <c r="E6" t="n">
-        <v>391</v>
+        <v>721</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>3306</v>
+        <v>2966</v>
       </c>
       <c r="E7" t="n">
-        <v>3306</v>
+        <v>2972</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="D9" t="n">
-        <v>5822</v>
+        <v>4933</v>
       </c>
       <c r="E9" t="n">
-        <v>6056</v>
+        <v>5083</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9614</v>
+        <v>0.9704999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/output/DROPOFF_diario.xlsx
+++ b/output/DROPOFF_diario.xlsx
@@ -475,7 +475,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,22 +484,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n">
-        <v>1459</v>
+        <v>2364</v>
       </c>
       <c r="E2" t="n">
-        <v>1831</v>
+        <v>2471</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.7968000000000001</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -577,10 +577,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>721</v>
+        <v>599</v>
       </c>
       <c r="E6" t="n">
-        <v>721</v>
+        <v>599</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -589,7 +589,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>2966</v>
+        <v>3494</v>
       </c>
       <c r="E7" t="n">
-        <v>2972</v>
+        <v>3535</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.998</v>
+        <v>0.9884000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,22 +646,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>379</v>
       </c>
       <c r="D9" t="n">
-        <v>4933</v>
+        <v>5042</v>
       </c>
       <c r="E9" t="n">
-        <v>5083</v>
+        <v>5421</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.9704999999999999</v>
+        <v>0.9301</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
